--- a/marketer_forms/002_sosyal_medya_i_erik_talep_formu--marketer_forms.xlsx
+++ b/marketer_forms/002_sosyal_medya_i_erik_talep_formu--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1134,8 +1134,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'photo'}</t>
+          <t>photo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Photo'}</t>
+          <t>Photo</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'post'}</t>
+          <t>post</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Post'}</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'everyone'}</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Everyone'}</t>
+          <t>Everyone</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Friends'}</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'declined'}</t>
+          <t>declined</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Declined'}</t>
+          <t>Declined</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'tag_1'}</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 1'}</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'tag_2'}</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 2'}</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'tag_1'}</t>
+          <t>tag_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 1'}</t>
+          <t>Tag 1</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'tag_2'}</t>
+          <t>tag_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Tag 2'}</t>
+          <t>Tag 2</t>
         </is>
       </c>
     </row>
